--- a/token_metrics/linda_1/delta_mode_0/eval_linda_delta0.xlsx
+++ b/token_metrics/linda_1/delta_mode_0/eval_linda_delta0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Università - Borsa di Ricerca\HDT Framework Repo\HumanDigitalTwin\token_metrics\linda_1\delta_mode_0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C213DED4-34BB-400A-81AD-C6E700867BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591A3A7C-DCA5-49F1-9293-8A5A7C4A2EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4282" yWindow="2520" windowWidth="16200" windowHeight="9855" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Queries" sheetId="1" r:id="rId1"/>
@@ -622,9 +622,6 @@
     <t xml:space="preserve">C </t>
   </si>
   <si>
-    <t>Triples (n relationships)</t>
-  </si>
-  <si>
     <t>FPR</t>
   </si>
   <si>
@@ -632,6 +629,9 @@
   </si>
   <si>
     <t>Accuracy Completeness</t>
+  </si>
+  <si>
+    <t>Triples</t>
   </si>
 </sst>
 </file>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B4" s="4">
         <f>IF(COUNTA(Queries!A2:A41)=0,0,SUM(Queries!L2:L41)/COUNTA(Queries!A2:A41))</f>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B5">
-        <v>148</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
@@ -2794,7 +2794,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B10" s="4" cm="1">
         <f t="array" ref="B10">IF(SUMPRODUCT(--(Queries!E2:E41&lt;&gt;"hallucination"))=0,"",1-SUMPRODUCT(--(Queries!E2:E41&lt;&gt;"hallucination"),--(((LOWER(TRIM(Queries!J2:J41))="unknown")+(TRIM(Queries!J2:J41)=""))&gt;0))/SUMPRODUCT(--(Queries!E2:E41&lt;&gt;"hallucination")))</f>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B12">
         <v>0</v>
